--- a/excel-jan-barcode/products_with_barcode.xlsx
+++ b/excel-jan-barcode/products_with_barcode.xlsx
@@ -9,7 +9,10 @@
   <sheets>
     <sheet name="商品リスト" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'商品リスト'!$A$1:$E$8</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'商品リスト'!$A$1:$E$8</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -29,15 +32,21 @@
       <b val="1"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDCE6F1"/>
+        <bgColor rgb="FFDCE6F1"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -45,24 +54,39 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB7B7B7"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB7B7B7"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB7B7B7"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB7B7B7"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -266,6 +290,56 @@
     </pic>
     <clientData/>
   </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>3</col>
+      <colOff>0</colOff>
+      <row>6</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1432560" cy="963168"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="6" name="Image 6" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId6"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>3</col>
+      <colOff>0</colOff>
+      <row>7</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1432560" cy="963168"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="7" name="Image 7" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId7"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
 </wsDr>
 </file>
 
@@ -556,16 +630,16 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:E6"/>
+  <dimension ref="A1:E8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
     <col width="32" customWidth="1" min="2" max="2"/>
     <col width="16" customWidth="1" min="3" max="3"/>
     <col width="30" customWidth="1" min="4" max="4"/>
-    <col width="46" customWidth="1" min="5" max="5"/>
+    <col width="50" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -609,6 +683,7 @@
           <t>4901111222236</t>
         </is>
       </c>
+      <c r="D2" s="5" t="n"/>
       <c r="E2" s="3" t="inlineStr"/>
     </row>
     <row r="3" ht="92" customHeight="1">
@@ -625,6 +700,7 @@
           <t>4502222333349</t>
         </is>
       </c>
+      <c r="D3" s="5" t="n"/>
       <c r="E3" s="3" t="inlineStr"/>
     </row>
     <row r="4" ht="92" customHeight="1">
@@ -641,6 +717,7 @@
           <t>4903333444458</t>
         </is>
       </c>
+      <c r="D4" s="5" t="n"/>
       <c r="E4" s="3" t="inlineStr">
         <is>
           <t>チェックデジットを 9 → 8 に自動修正(元データのチェックデジットが誤っていた可能性があります)</t>
@@ -661,6 +738,7 @@
           <t>4564444555565</t>
         </is>
       </c>
+      <c r="D5" s="5" t="n"/>
       <c r="E5" s="3" t="inlineStr"/>
     </row>
     <row r="6" ht="92" customHeight="1">
@@ -677,10 +755,48 @@
           <t>4905555666670</t>
         </is>
       </c>
+      <c r="D6" s="5" t="n"/>
       <c r="E6" s="3" t="inlineStr"/>
     </row>
+    <row r="7" ht="92" customHeight="1">
+      <c r="A7" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>使い切り除草剤 お試しミニパック</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>49012347</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="n"/>
+      <c r="E7" s="3" t="inlineStr"/>
+    </row>
+    <row r="8" ht="92" customHeight="1">
+      <c r="A8" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>園芸用手袋 お試しサイズ</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>49123456</t>
+        </is>
+      </c>
+      <c r="D8" s="5" t="n"/>
+      <c r="E8" s="3" t="inlineStr"/>
+    </row>
   </sheetData>
+  <autoFilter ref="A1:E8"/>
+  <printOptions horizontalCentered="0"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" scale="100" fitToHeight="0" fitToWidth="0"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>